--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487844_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487844_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0883</v>
+        <v>6.8996</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6737</v>
+        <v>3.6318</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4146</v>
+        <v>3.2678</v>
       </c>
       <c r="G2" t="n">
         <v>4.0428</v>
@@ -610,13 +610,13 @@
         <v>3.538</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1912</v>
+        <v>0.0025</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4096</v>
+        <v>0.3677</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2184</v>
+        <v>-0.3652</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2958</v>
+        <v>5.9668</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9825</v>
+        <v>4.0058</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3134</v>
+        <v>1.961</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0622</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7066</v>
+        <v>0.3776</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2048</v>
+        <v>0.2281</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5018</v>
+        <v>0.1495</v>
       </c>
       <c r="V3" t="n">
         <v>6.6514</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1754</v>
+        <v>4.7713</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5468</v>
+        <v>4.7904</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3714</v>
+        <v>-0.0191</v>
       </c>
       <c r="G4" t="n">
         <v>1.9678</v>
@@ -766,13 +766,13 @@
         <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1046</v>
+        <v>0.7005</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0095</v>
+        <v>1.253</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9048</v>
+        <v>-0.5525</v>
       </c>
       <c r="V4" t="n">
         <v>0.23</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7875</v>
+        <v>2.3908</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.536</v>
+        <v>-0.7859</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3235</v>
+        <v>3.1768</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0525</v>
@@ -844,13 +844,13 @@
         <v>3.1218</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5356</v>
+        <v>0.0677</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7458</v>
+        <v>0.0043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2102</v>
+        <v>0.0634</v>
       </c>
       <c r="V5" t="n">
         <v>2.3351</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7271</v>
+        <v>1.9517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2939</v>
+        <v>0.401</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4333</v>
+        <v>1.5507</v>
       </c>
       <c r="G6" t="n">
         <v>1.3536</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6889</v>
+        <v>-0.4643</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0529</v>
+        <v>0.0543</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6361</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.23</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06950000000000001</v>
+        <v>1.1952</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0004</v>
+        <v>1.7738</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.5786</v>
       </c>
       <c r="G7" t="n">
         <v>0.3321</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9734</v>
+        <v>0.1524</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3138</v>
+        <v>0.4596</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6595</v>
+        <v>-0.3072</v>
       </c>
       <c r="V7" t="n">
         <v>1.7513</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8286</v>
+        <v>-0.0617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7274</v>
+        <v>1.4356</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.556</v>
+        <v>-1.4973</v>
       </c>
       <c r="G8" t="n">
         <v>-3.16</v>
@@ -1078,13 +1078,13 @@
         <v>2.7055</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1442</v>
+        <v>0.6227</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0215</v>
+        <v>0.7297</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1657</v>
+        <v>-0.107</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8923</v>
+        <v>-0.7617</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4105</v>
+        <v>-2.9179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5182</v>
+        <v>2.1562</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4529</v>
+        <v>-1.7782</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8235</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3707</v>
+        <v>-2.4158</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0934</v>
+        <v>-2.0883</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3866</v>
+        <v>-0.0236</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2932</v>
+        <v>-2.0647</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3595</v>
+        <v>0.3102</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4369</v>
+        <v>0.6612</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9225</v>
+        <v>-0.351</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>2.4974</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9768</v>
+        <v>-0.2104</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7641</v>
+        <v>0.211</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2127</v>
+        <v>-0.4214</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8581</v>
+        <v>-2.1019</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6913</v>
+        <v>-2.2678</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8333</v>
+        <v>0.1659</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7782</v>
+        <v>-2.4529</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6375999999999999</v>
+        <v>-2.8235</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4158</v>
+        <v>0.3707</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0883</v>
+        <v>-1.0934</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0236</v>
+        <v>-2.3866</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0647</v>
+        <v>1.2932</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3102</v>
+        <v>-1.3595</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6612</v>
+        <v>-0.4369</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.351</v>
+        <v>-0.9225</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4974</v>
+        <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3068</v>
+        <v>0.7672</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5624</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7444</v>
+        <v>-0.1396</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3346</v>
+        <v>-2.3677</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.774</v>
+        <v>-3.6016</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4394</v>
+        <v>1.2339</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9458</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.503</v>
+        <v>0.4699</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1924</v>
+        <v>0.3648</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3106</v>
+        <v>0.1051</v>
       </c>
       <c r="V11" t="n">
         <v>0.8137</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.23</v>
+        <v>17.8824</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8129</v>
+        <v>6.465200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4174</v>
+        <v>11.4173</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7553</v>
@@ -1378,7 +1378,7 @@
         <v>-2.4919</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.612400000000001</v>
+        <v>-2.6124</v>
       </c>
       <c r="P12" t="n">
         <v>5.203</v>
@@ -1390,13 +1390,13 @@
         <v>21.8524</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8333</v>
+        <v>2.4858</v>
       </c>
       <c r="T12" t="n">
-        <v>3.927</v>
+        <v>4.5793</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0936</v>
+        <v>-2.0935</v>
       </c>
       <c r="V12" t="n">
         <v>12.949</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4467</v>
+        <v>6.0031</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1713</v>
+        <v>4.4928</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2754</v>
+        <v>1.5103</v>
       </c>
       <c r="G13" t="n">
         <v>1.9926</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5241</v>
+        <v>-0.9677</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3171</v>
+        <v>0.0043</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2069</v>
+        <v>-0.972</v>
       </c>
       <c r="V13" t="n">
         <v>2.6889</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3072</v>
+        <v>-0.0354</v>
       </c>
       <c r="E14" t="n">
-        <v>0.926</v>
+        <v>0.5216</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6188</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3768</v>
+        <v>0.2249</v>
       </c>
       <c r="H14" t="n">
-        <v>0.015</v>
+        <v>-0.7784</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3919</v>
+        <v>1.0034</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0192</v>
+        <v>1.5723</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0192</v>
+        <v>0.7159</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.396</v>
+        <v>-1.3474</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0041</v>
+        <v>-1.4943</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3919</v>
+        <v>0.147</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5383</v>
+        <v>-0.2604</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9474</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4091</v>
+        <v>-0.3314</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4732</v>
+        <v>-0.166</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8911</v>
+        <v>2.3197</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3643</v>
+        <v>-2.4857</v>
       </c>
       <c r="G15" t="n">
         <v>4.8906</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2786</v>
+        <v>0.0287</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2519</v>
+        <v>0.1767</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0267</v>
+        <v>-0.148</v>
       </c>
       <c r="V15" t="n">
         <v>-5.5016</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5012</v>
+        <v>-0.3452</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5216</v>
+        <v>-2.054</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0228</v>
+        <v>1.7088</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2249</v>
+        <v>-0.014</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7784</v>
+        <v>-0.4475</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0034</v>
+        <v>0.4335</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5723</v>
+        <v>-0.067</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7159</v>
+        <v>-0.676</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.609</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3474</v>
+        <v>0.0529</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4943</v>
+        <v>0.2284</v>
       </c>
       <c r="O16" t="n">
-        <v>0.147</v>
+        <v>-0.1755</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-3.1218</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7262</v>
+        <v>0.3743</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0328</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7972</v>
+        <v>0.4071</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
         <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.3983</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0784</v>
+        <v>0.1855</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6132</v>
+        <v>-0.5838</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5544</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0196</v>
+        <v>0.1561</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1072</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1462</v>
+        <v>-0.6993</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8041</v>
+        <v>-0.2527</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6579</v>
+        <v>-0.4466</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.014</v>
+        <v>-0.3768</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4475</v>
+        <v>0.015</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4335</v>
+        <v>-0.3919</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.067</v>
+        <v>0.0192</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.676</v>
+        <v>0.0192</v>
       </c>
       <c r="L18" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0529</v>
+        <v>-0.396</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2284</v>
+        <v>-0.0041</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1755</v>
+        <v>-0.3919</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8731</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4266</v>
+        <v>0.5319</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7829</v>
+        <v>0.7687</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3563</v>
+        <v>-0.2368</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6546</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3944</v>
+        <v>-1.3349</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2602</v>
+        <v>0.529</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.419</v>
+        <v>1.3025</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8615</v>
+        <v>0.8404</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4425</v>
+        <v>0.4621</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8107</v>
+        <v>0.2372</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1431</v>
+        <v>0.1343</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3324</v>
+        <v>0.1028</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6083</v>
+        <v>1.0653</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2816</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8899</v>
+        <v>0.3592</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8269</v>
+        <v>-0.1895</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2051</v>
+        <v>-0.5314</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6218</v>
+        <v>0.3419</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6899</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0869</v>
+        <v>-2.4154</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9778</v>
+        <v>-0.9211</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1091</v>
+        <v>-1.4942</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3025</v>
+        <v>-0.2204</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8404</v>
+        <v>-0.1535</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4621</v>
+        <v>-0.0669</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2372</v>
+        <v>0.0776</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1343</v>
+        <v>0.0384</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1028</v>
+        <v>0.0392</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0653</v>
+        <v>-0.298</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7060999999999999</v>
+        <v>-0.1919</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3592</v>
+        <v>-0.1061</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4705</v>
+        <v>-0.1949</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1744</v>
+        <v>0.0419</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2962</v>
+        <v>-0.2368</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5519</v>
+        <v>-2.941</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0283</v>
+        <v>-3.6537</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5236</v>
+        <v>0.7128</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2204</v>
+        <v>0.5844</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1535</v>
+        <v>0.5142</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0669</v>
+        <v>0.0702</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0776</v>
+        <v>0.2947</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0384</v>
+        <v>0.1919</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>0.1028</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.298</v>
+        <v>0.2897</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1919</v>
+        <v>0.3223</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1061</v>
+        <v>-0.0326</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8325</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-4.3705</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3314</v>
+        <v>0.5558</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2662</v>
+        <v>0.1338</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1675</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8897</v>
+        <v>-3.623</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2337</v>
+        <v>-5.3409</v>
       </c>
       <c r="F22" t="n">
-        <v>1.344</v>
+        <v>1.7179</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8198</v>
@@ -2170,13 +2170,13 @@
         <v>2.4974</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0876</v>
+        <v>-0.8209</v>
       </c>
       <c r="T22" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1586</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1498</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0331</v>
+        <v>-3.6436</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0824</v>
+        <v>-3.0018</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0493</v>
+        <v>-0.6418</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5844</v>
+        <v>-1.419</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5142</v>
+        <v>-1.8615</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0702</v>
+        <v>0.4425</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2947</v>
+        <v>-0.8107</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1919</v>
+        <v>-2.1431</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1028</v>
+        <v>1.3324</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2897</v>
+        <v>-0.6083</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3223</v>
+        <v>0.2816</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0326</v>
+        <v>-0.8899</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9137</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.3705</v>
+        <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5363</v>
+        <v>0.8378</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0066</v>
+        <v>0.5977</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.2401</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1123</v>
+        <v>-6.0169</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.485</v>
+        <v>-2.3779</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6273</v>
+        <v>-3.639</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8353</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1631</v>
+        <v>0.2585</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3972</v>
+        <v>0.5044</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2341</v>
+        <v>-0.2459</v>
       </c>
       <c r="V24" t="n">
         <v>-3.8564</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.23</v>
+        <v>-15.0869</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.4173</v>
+        <v>-11.4174</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8127</v>
+        <v>-3.6693</v>
       </c>
       <c r="G25" t="n">
         <v>2.7553</v>
@@ -2380,10 +2380,10 @@
         <v>5.104300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4919</v>
+        <v>2.491900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>2.612400000000001</v>
+        <v>2.6124</v>
       </c>
       <c r="M25" t="n">
         <v>-2.3491</v>
@@ -2395,7 +2395,7 @@
         <v>-1.0407</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.203200000000001</v>
+        <v>-5.2032</v>
       </c>
       <c r="Q25" t="n">
         <v>-21.8525</v>
@@ -2404,13 +2404,13 @@
         <v>16.6492</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.833399999999999</v>
+        <v>0.3097000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.093599999999999</v>
+        <v>2.0936</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.927</v>
+        <v>-1.7839</v>
       </c>
       <c r="V25" t="n">
         <v>-12.949</v>
